--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peera/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peera/Downloads/lab_exam_v3_final_updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6DA9BB-4080-C842-B712-5F2313311BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EDB40C-0EA6-AB40-97CD-2BD9ADC4FD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6620" yWindow="760" windowWidth="22100" windowHeight="17240" xr2:uid="{EB430854-A694-1440-8F23-D31C00125C00}"/>
+    <workbookView xWindow="6620" yWindow="740" windowWidth="22100" windowHeight="17240" xr2:uid="{EB430854-A694-1440-8F23-D31C00125C00}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -372,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -382,7 +382,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -776,9 +775,9 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="9" t="str">
+      <c r="G2" s="3" t="str">
         <f ca="1">"M"&amp;TEXT(RANDBETWEEN(0,99999),"00000")</f>
-        <v>M17155</v>
+        <v>M65211</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>13</v>
@@ -809,9 +808,9 @@
       <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="9" t="str">
+      <c r="G3" s="3" t="str">
         <f t="shared" ref="G3:G66" ca="1" si="0">"M"&amp;TEXT(RANDBETWEEN(0,99999),"00000")</f>
-        <v>M13949</v>
+        <v>M23129</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>13</v>
@@ -838,9 +837,9 @@
       <c r="F4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="9" t="str">
+      <c r="G4" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M31586</v>
+        <v>M07032</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>13</v>
@@ -867,9 +866,9 @@
       <c r="F5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="9" t="str">
+      <c r="G5" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M94214</v>
+        <v>M86524</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>13</v>
@@ -896,9 +895,9 @@
       <c r="F6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="9" t="str">
+      <c r="G6" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M29515</v>
+        <v>M91982</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>13</v>
@@ -925,9 +924,9 @@
       <c r="F7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="9" t="str">
+      <c r="G7" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M83988</v>
+        <v>M21317</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>13</v>
@@ -954,9 +953,9 @@
       <c r="F8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="9" t="str">
+      <c r="G8" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M20168</v>
+        <v>M84252</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>13</v>
@@ -983,9 +982,9 @@
       <c r="F9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="9" t="str">
+      <c r="G9" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M58255</v>
+        <v>M54218</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>13</v>
@@ -1012,9 +1011,9 @@
       <c r="F10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="9" t="str">
+      <c r="G10" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M13970</v>
+        <v>M79291</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>13</v>
@@ -1041,9 +1040,9 @@
       <c r="F11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="9" t="str">
+      <c r="G11" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M31621</v>
+        <v>M79411</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>13</v>
@@ -1070,9 +1069,9 @@
       <c r="F12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="9" t="str">
+      <c r="G12" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M86945</v>
+        <v>M66510</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>13</v>
@@ -1099,9 +1098,9 @@
       <c r="F13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="9" t="str">
+      <c r="G13" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M71666</v>
+        <v>M42287</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>13</v>
@@ -1128,9 +1127,9 @@
       <c r="F14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="9" t="str">
+      <c r="G14" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M25292</v>
+        <v>M11453</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>13</v>
@@ -1157,9 +1156,9 @@
       <c r="F15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="9" t="str">
+      <c r="G15" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M51657</v>
+        <v>M01910</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>13</v>
@@ -1186,9 +1185,9 @@
       <c r="F16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="9" t="str">
+      <c r="G16" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M74294</v>
+        <v>M04230</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>13</v>
@@ -1215,9 +1214,9 @@
       <c r="F17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="9" t="str">
+      <c r="G17" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M28787</v>
+        <v>M87369</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>13</v>
@@ -1244,9 +1243,9 @@
       <c r="F18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="9" t="str">
+      <c r="G18" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M72162</v>
+        <v>M88329</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>13</v>
@@ -1273,9 +1272,9 @@
       <c r="F19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="9" t="str">
+      <c r="G19" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M97882</v>
+        <v>M38897</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>13</v>
@@ -1302,9 +1301,9 @@
       <c r="F20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="9" t="str">
+      <c r="G20" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M39307</v>
+        <v>M04236</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>13</v>
@@ -1331,9 +1330,9 @@
       <c r="F21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="9" t="str">
+      <c r="G21" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M64768</v>
+        <v>M22283</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>13</v>
@@ -1360,9 +1359,9 @@
       <c r="F22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="9" t="str">
+      <c r="G22" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M91362</v>
+        <v>M61342</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>13</v>
@@ -1389,9 +1388,9 @@
       <c r="F23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G23" s="9" t="str">
+      <c r="G23" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M33305</v>
+        <v>M17357</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>13</v>
@@ -1418,9 +1417,9 @@
       <c r="F24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G24" s="9" t="str">
+      <c r="G24" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M25560</v>
+        <v>M59777</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>13</v>
@@ -1435,9 +1434,9 @@
       <c r="D25" s="3"/>
       <c r="E25" s="8"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="9" t="str">
+      <c r="G25" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M74949</v>
+        <v>M14120</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -1462,9 +1461,9 @@
       <c r="F26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="9" t="str">
+      <c r="G26" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M02134</v>
+        <v>M49048</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>39</v>
@@ -1483,9 +1482,9 @@
       <c r="D27" s="3"/>
       <c r="E27" s="8"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="9" t="str">
+      <c r="G27" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M94367</v>
+        <v>M02280</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -1510,9 +1509,9 @@
       <c r="F28" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="9" t="str">
+      <c r="G28" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M92263</v>
+        <v>M20689</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -1525,9 +1524,9 @@
       <c r="D29" s="3"/>
       <c r="E29" s="8"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="9" t="str">
+      <c r="G29" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M43774</v>
+        <v>M63926</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -1552,9 +1551,9 @@
       <c r="F30" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="9" t="str">
+      <c r="G30" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M75459</v>
+        <v>M60149</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>41</v>
@@ -1573,9 +1572,9 @@
       <c r="D31" s="3"/>
       <c r="E31" s="8"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="9" t="str">
+      <c r="G31" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M37624</v>
+        <v>M92869</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -1600,9 +1599,9 @@
       <c r="F32" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="9" t="str">
+      <c r="G32" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M26862</v>
+        <v>M46063</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -1615,9 +1614,9 @@
       <c r="D33" s="3"/>
       <c r="E33" s="8"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="9" t="str">
+      <c r="G33" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M06858</v>
+        <v>M50244</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -1630,9 +1629,9 @@
       <c r="D34" s="3"/>
       <c r="E34" s="8"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="9" t="str">
+      <c r="G34" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M16035</v>
+        <v>M71468</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -1645,9 +1644,9 @@
       <c r="D35" s="3"/>
       <c r="E35" s="8"/>
       <c r="F35" s="3"/>
-      <c r="G35" s="9" t="str">
+      <c r="G35" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M94702</v>
+        <v>M07415</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -1672,9 +1671,9 @@
       <c r="F36" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="9" t="str">
+      <c r="G36" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M89324</v>
+        <v>M26099</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>44</v>
@@ -1705,9 +1704,9 @@
       <c r="F37" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="9" t="str">
+      <c r="G37" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M66714</v>
+        <v>M32022</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>46</v>
@@ -1738,9 +1737,9 @@
       <c r="F38" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="9" t="str">
+      <c r="G38" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M96212</v>
+        <v>M89587</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>48</v>
@@ -1771,9 +1770,9 @@
       <c r="F39" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="9" t="str">
+      <c r="G39" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M17103</v>
+        <v>M04969</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>50</v>
@@ -1804,9 +1803,9 @@
       <c r="F40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="9" t="str">
+      <c r="G40" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M30800</v>
+        <v>M35446</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>52</v>
@@ -1837,9 +1836,9 @@
       <c r="F41" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="9" t="str">
+      <c r="G41" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M05003</v>
+        <v>M35324</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>56</v>
@@ -1870,9 +1869,9 @@
       <c r="F42" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="9" t="str">
+      <c r="G42" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M47245</v>
+        <v>M11600</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>44</v>
@@ -1903,9 +1902,9 @@
       <c r="F43" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="9" t="str">
+      <c r="G43" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M39232</v>
+        <v>M24055</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>59</v>
@@ -1936,9 +1935,9 @@
       <c r="F44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G44" s="9" t="str">
+      <c r="G44" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M96416</v>
+        <v>M90056</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>61</v>
@@ -1969,9 +1968,9 @@
       <c r="F45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G45" s="9" t="str">
+      <c r="G45" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M02271</v>
+        <v>M69769</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>63</v>
@@ -2002,9 +2001,9 @@
       <c r="F46" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G46" s="9" t="str">
+      <c r="G46" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M70310</v>
+        <v>M67141</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>50</v>
@@ -2035,9 +2034,9 @@
       <c r="F47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G47" s="9" t="str">
+      <c r="G47" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M90451</v>
+        <v>M31339</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>66</v>
@@ -2068,9 +2067,9 @@
       <c r="F48" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G48" s="9" t="str">
+      <c r="G48" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M91414</v>
+        <v>M79337</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>68</v>
@@ -2101,9 +2100,9 @@
       <c r="F49" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G49" s="9" t="str">
+      <c r="G49" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M38444</v>
+        <v>M27685</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>70</v>
@@ -2134,9 +2133,9 @@
       <c r="F50" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="9" t="str">
+      <c r="G50" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M21985</v>
+        <v>M97801</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>74</v>
@@ -2163,9 +2162,9 @@
       <c r="F51" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G51" s="9" t="str">
+      <c r="G51" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M90480</v>
+        <v>M71890</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>75</v>
@@ -2192,9 +2191,9 @@
       <c r="F52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G52" s="9" t="str">
+      <c r="G52" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M53193</v>
+        <v>M96410</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>61</v>
@@ -2221,9 +2220,9 @@
       <c r="F53" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G53" s="9" t="str">
+      <c r="G53" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M75785</v>
+        <v>M36480</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>76</v>
@@ -2250,9 +2249,9 @@
       <c r="F54" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G54" s="9" t="str">
+      <c r="G54" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M56593</v>
+        <v>M78154</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>63</v>
@@ -2279,9 +2278,9 @@
       <c r="F55" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G55" s="9" t="str">
+      <c r="G55" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M87862</v>
+        <v>M44997</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>75</v>
@@ -2308,9 +2307,9 @@
       <c r="F56" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G56" s="9" t="str">
+      <c r="G56" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M11321</v>
+        <v>M58960</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>77</v>
@@ -2337,9 +2336,9 @@
       <c r="F57" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G57" s="9" t="str">
+      <c r="G57" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M42218</v>
+        <v>M24222</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>78</v>
@@ -2366,9 +2365,9 @@
       <c r="F58" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G58" s="9" t="str">
+      <c r="G58" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M87533</v>
+        <v>M24526</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>74</v>
@@ -2395,9 +2394,9 @@
       <c r="F59" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G59" s="9" t="str">
+      <c r="G59" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M16333</v>
+        <v>M66764</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>50</v>
@@ -2424,9 +2423,9 @@
       <c r="F60" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G60" s="9" t="str">
+      <c r="G60" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M84460</v>
+        <v>M72040</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>44</v>
@@ -2453,9 +2452,9 @@
       <c r="F61" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G61" s="9" t="str">
+      <c r="G61" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M00009</v>
+        <v>M80273</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -2480,9 +2479,9 @@
       <c r="F62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G62" s="9" t="str">
+      <c r="G62" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M29011</v>
+        <v>M32508</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>61</v>
@@ -2509,9 +2508,9 @@
       <c r="F63" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="9" t="str">
+      <c r="G63" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M56532</v>
+        <v>M64560</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>59</v>
@@ -2538,9 +2537,9 @@
       <c r="F64" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G64" s="9" t="str">
+      <c r="G64" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M39942</v>
+        <v>M30687</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>81</v>
@@ -2567,9 +2566,9 @@
       <c r="F65" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G65" s="9" t="str">
+      <c r="G65" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M16932</v>
+        <v>M35794</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>66</v>
@@ -2596,9 +2595,9 @@
       <c r="F66" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G66" s="9" t="str">
+      <c r="G66" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>M13247</v>
+        <v>M45241</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>78</v>
@@ -2625,9 +2624,9 @@
       <c r="F67" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G67" s="9" t="str">
+      <c r="G67" s="3" t="str">
         <f t="shared" ref="G67:G89" ca="1" si="1">"M"&amp;TEXT(RANDBETWEEN(0,99999),"00000")</f>
-        <v>M51072</v>
+        <v>M85239</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>68</v>
@@ -2654,9 +2653,9 @@
       <c r="F68" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G68" s="9" t="str">
+      <c r="G68" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M30211</v>
+        <v>M72561</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>70</v>
@@ -2683,9 +2682,9 @@
       <c r="F69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G69" s="9" t="str">
+      <c r="G69" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M21295</v>
+        <v>M53340</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>63</v>
@@ -2712,9 +2711,9 @@
       <c r="F70" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G70" s="9" t="str">
+      <c r="G70" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M31669</v>
+        <v>M75014</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>74</v>
@@ -2741,9 +2740,9 @@
       <c r="F71" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G71" s="9" t="str">
+      <c r="G71" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M89750</v>
+        <v>M39012</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>76</v>
@@ -2770,9 +2769,9 @@
       <c r="F72" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="9" t="str">
+      <c r="G72" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M13650</v>
+        <v>M19509</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
@@ -2797,9 +2796,9 @@
       <c r="F73" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G73" s="9" t="str">
+      <c r="G73" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M53337</v>
+        <v>M11449</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>75</v>
@@ -2826,9 +2825,9 @@
       <c r="F74" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G74" s="9" t="str">
+      <c r="G74" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M25117</v>
+        <v>M27707</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>74</v>
@@ -2855,9 +2854,9 @@
       <c r="F75" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G75" s="9" t="str">
+      <c r="G75" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M66292</v>
+        <v>M95607</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>46</v>
@@ -2884,9 +2883,9 @@
       <c r="F76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="9" t="str">
+      <c r="G76" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M16296</v>
+        <v>M60316</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>61</v>
@@ -2913,9 +2912,9 @@
       <c r="F77" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G77" s="9" t="str">
+      <c r="G77" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M95294</v>
+        <v>M78023</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>63</v>
@@ -2946,9 +2945,9 @@
       <c r="F78" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G78" s="9" t="str">
+      <c r="G78" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M32214</v>
+        <v>M82459</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3">
@@ -2977,9 +2976,9 @@
       <c r="F79" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G79" s="9" t="str">
+      <c r="G79" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M07793</v>
+        <v>M16270</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>63</v>
@@ -3006,9 +3005,9 @@
       <c r="F80" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G80" s="9" t="str">
+      <c r="G80" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M48191</v>
+        <v>M03141</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>70</v>
@@ -3035,9 +3034,9 @@
       <c r="F81" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G81" s="9" t="str">
+      <c r="G81" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M39876</v>
+        <v>M64581</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>13</v>
@@ -3064,9 +3063,9 @@
       <c r="F82" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G82" s="9" t="str">
+      <c r="G82" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M47781</v>
+        <v>M89187</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
@@ -3091,9 +3090,9 @@
       <c r="F83" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G83" s="9" t="str">
+      <c r="G83" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M56806</v>
+        <v>M52879</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>70</v>
@@ -3120,9 +3119,9 @@
       <c r="F84" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G84" s="9" t="str">
+      <c r="G84" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M52214</v>
+        <v>M91266</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>63</v>
@@ -3149,9 +3148,9 @@
       <c r="F85" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G85" s="9" t="str">
+      <c r="G85" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M22913</v>
+        <v>M43663</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>77</v>
@@ -3178,9 +3177,9 @@
       <c r="F86" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G86" s="9" t="str">
+      <c r="G86" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M41472</v>
+        <v>M55135</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>63</v>
@@ -3207,9 +3206,9 @@
       <c r="F87" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G87" s="9" t="str">
+      <c r="G87" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M38156</v>
+        <v>M38894</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>70</v>
@@ -3236,9 +3235,9 @@
       <c r="F88" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G88" s="9" t="str">
+      <c r="G88" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M94447</v>
+        <v>M27468</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
@@ -3263,9 +3262,9 @@
       <c r="F89" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="9" t="str">
+      <c r="G89" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>M12951</v>
+        <v>M44456</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>13</v>
